--- a/output/第10期計画_施策体系新旧対照表.xlsx
+++ b/output/第10期計画_施策体系新旧対照表.xlsx
@@ -1929,7 +1929,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>第9期は未調整率。第10期は年齢調整済へ変更するため時系列が接続しない。第9期の達成度は未調整率で評価し、H01とは別管理とする。</t>
+          <t>第9期は未調整率。第10期は年齢調整済へ変更するため時系列が接続しない。第9期の達成度は未調整率で評価し、H01とは別管理とする。なお全体の認定率がH30 20.8％→R8 21.8％と上昇する一方、75歳以上は35.3％→33.5％、85歳以上はR2 63.7％→61.6％と低下しており、年齢調整の必要性は実データで裏付けられている。</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>同上。介護人材実態調査で代替可能</t>
+          <t>介護人材実態調査は仕様書の対象調査に含まれるが、第9期の同調査に「必要常勤換算数」の設問は確認できない。第10期の調査票を確認する（修正指示書C-16）。</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>要検討</t>
+          <t>設問を要確認</t>
         </is>
       </c>
     </row>
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>同上。「採用後12か月時点の在職」を追跡する設問がない。年間離職率での代替を検討する。</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>要検討</t>
+          <t>設問を要確認</t>
         </is>
       </c>
     </row>
@@ -2484,19 +2484,19 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>BCPの実行可否を評価。データ源の確保が必要</t>
+          <t>実績指標のため事象がなければ測定機会が生じない。BCP策定率・訓練実施率・相互応援協定数といった体制指標への組替えを検討する（修正指示書B-20）。</t>
         </is>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>要検討</t>
+          <t>指標設計を要検討</t>
         </is>
       </c>
     </row>
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>注1）第9期の代表KPI4項目のうち、そのまま接続できるのはH02・H04の2項目のみです。H01は未調整率から年齢調整済率への変更、H05は通いの場から社会参加への拡張により、時系列が断絶します。注2）H07・H08・H12・H13・H14・H16の6項目は、調査の実施可否によりデータ源が確保できない可能性があります（修正指示書A-7・A-9）。注3）第9期の達成度評価は第9期の定義で行い、第10期のKPIは新たな基準値から開始することを推奨します。計画本文には両者を併記し、断絶の理由を注記してください。</t>
+          <t>注1）第9期の代表KPI4項目のうち、そのまま接続できるのはH02・H04の2項目のみです。H01は未調整率から年齢調整済率への変更、H05は通いの場から社会参加への拡張により、時系列が断絶します。注2）データ源の確保状況を個別に評価した結果、令和9年度当初から実測できる見通しが立っているのはH01・H02・H04・H05・H06・H11・H13・H15の8項目です。H07・H08・H12・H16の4項目は業務範囲の決定が必要（修正指示書A-7・A-9）、H09・H10の2項目は3町の業務記録の様式整備が必要（同B-19）、H14は設問の追加又は代替が必要（同C-16）、H03は認定台帳からの抽出可否の確認が必要（同C-15）です。詳細は妥当性検証報告書15シートを参照してください。注3）第9期の達成度評価は第9期の定義で行い、第10期のKPIは新たな基準値から開始することを推奨します。計画本文には両者を併記し、断絶の理由を注記してください。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_施策体系新旧対照表.xlsx
+++ b/output/第10期計画_施策体系新旧対照表.xlsx
@@ -1924,17 +1924,17 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>16.7％／18.4％</t>
+          <t>9.25％（W144・R5調査）</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>第9期は未調整率。第10期は年齢調整済へ変更するため時系列が接続しない。第9期の達成度は未調整率で評価し、H01とは別管理とする。なお全体の認定率がH30 20.8％→R8 21.8％と上昇する一方、75歳以上は35.3％→33.5％、85歳以上はR2 63.7％→61.6％と低下しており、年齢調整の必要性は実データで裏付けられている。</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>採用系列を要決定</t>
+          <t>第9期は未調整率。第10期は年齢調整済へ変更するため時系列が接続しない。第9期の達成度は未調整率で評価し、H01とは別管理とする。なお全体の認定率がH30 20.8％→R8 21.8％と上昇する一方、75歳以上は35.3％→33.5％、85歳以上はR2 63.7％→61.6％と低下しており、年齢調整の必要性は実データで裏付けられている。データ源は見える化W144（保険者機能強化推進交付金 評価指標Ⅳ-5「性・年齢調整済み要介護2以上の認定率」）を推奨する。国が全保険者を共通の方法で毎年算定しており、全国8.99％・北海道8.59％と直接比較できるため、B5-aの2系列（16.7％／18.4％）の選択問題が解消する。変化率は大雪＋1.76に対し全国▲0.37・北海道▲1.71で大雪のみ上昇しているため、目標は「維持」ではなく「全国平均以下への低下」とする。</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>データ源を確保</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>職種別欠員率</t>
+          <t>職種別従事者数の推移（旧・職種別欠員率）</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -2368,17 +2368,17 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>535.17人（認定者1万対・R6）</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>介護人材実態調査は仕様書の対象調査に含まれるが、第9期の同調査に「必要常勤換算数」の設問は確認できない。第10期の調査票を確認する（修正指示書C-16）。</t>
+          <t>「必要常勤換算数」のデータ源であった見える化H1・H2はデータ登録がなく提供不可であることが確定したため、欠員率は算定できない。M2-a〜m（従事者数・13サービス・H29〜R6）の受領により、「職種別従事者数（認定者1万対）の推移」へ定義を改める。介護老人福祉施設では准看護師7人→3人、生活相談員5人→3人、機能訓練指導員2人→1人と特定職種が減少している（修正指示書C-16）。</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>設問を要確認</t>
+          <t>定義変更を要決定</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>採用者1年定着率</t>
+          <t>採用率と離職率の差（旧・採用者1年定着率）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>同上。「採用後12か月時点の在職」を追跡する設問がない。年間離職率での代替を検討する。</t>
+          <t>「採用後12か月時点の在職」を追跡する設問がない。北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）へ改め、第9期の介護人材実態調査の採用者数・退職者数から算定する。北海道は1.0％（R3）→全国平均以上（R8）。</t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t>設問を要確認</t>
+          <t>定義変更を要決定</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
     <row r="22" ht="40" customHeight="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>注1）第9期の代表KPI4項目のうち、そのまま接続できるのはH02・H04の2項目のみです。H01は未調整率から年齢調整済率への変更、H05は通いの場から社会参加への拡張により、時系列が断絶します。注2）データ源の確保状況を個別に評価した結果、令和9年度当初から実測できる見通しが立っているのはH01・H02・H04・H05・H06・H11・H13・H15の8項目です。H07・H08・H12・H16の4項目は業務範囲の決定が必要（修正指示書A-7・A-9）、H09・H10の2項目は3町の業務記録の様式整備が必要（同B-19）、H14は設問の追加又は代替が必要（同C-16）、H03は認定台帳からの抽出可否の確認が必要（同C-15）です。詳細は妥当性検証報告書15シートを参照してください。注3）第9期の達成度評価は第9期の定義で行い、第10期のKPIは新たな基準値から開始することを推奨します。計画本文には両者を併記し、断絶の理由を注記してください。</t>
+          <t>注1）第9期の代表KPI4項目のうち、そのまま接続できるのはH02・H04の2項目のみです。H01は未調整率から年齢調整済率への変更、H05は通いの場から社会参加への拡張により、時系列が断絶します。注2）データ源の確保状況を個別に評価した結果、令和9年度当初から実測できる見通しが立っているのはH01・H02・H04・H05・H06・H11・H13・H15の8項目です。H07・H08・H12・H16の4項目は業務範囲の決定が必要（修正指示書A-7・A-9）、H09・H10の2項目は3町の業務記録の様式整備が必要（同B-19）、H13・H14は定義変更の決定が必要（同C-16）、H03は認定台帳からの抽出可否の確認が必要（同C-15）です。注2-2）令和8年7月29日の見える化の追加受領（W144・M2系列）により、H01のデータ源が確定し、H13・H14の代替手段が特定されました。一方、H1・H2（介護人材の必要数）は大雪についてデータ登録がなく提供不可であることが確定しております。詳細は妥当性検証報告書15シートを参照してください。注3）第9期の達成度評価は第9期の定義で行い、第10期のKPIは新たな基準値から開始することを推奨します。計画本文には両者を併記し、断絶の理由を注記してください。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_施策体系新旧対照表.xlsx
+++ b/output/第10期計画_施策体系新旧対照表.xlsx
@@ -601,7 +601,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>第9期19施策と第10期施策の対応。評価可能性と修正方向を併記</t>
+          <t>第9期19施策と第10期施策の対応。計画記載上の評価可能性と修正方向を併記</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第9期計画 第5章「施策の展開」の19施策を母数とする。評価可能性は素案第9稿 表13による</t>
+          <t>第9期計画 第5章「施策の展開」の19施策を母数とする。「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定であり、事業が実際に実施されたか、効果があったかを評価したものではない（レッドチームレビュー No.11）。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。判定は素案第9稿 表13による</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,8 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>評価可能性</t>
+          <t>計画記載上の
+評価可能性</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1535,7 +1536,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>注1）評価可能性は素案第9稿 表13による。部分評価可能6施策（1-1・1-3・2-2・3-1・4-2・4-3）、指標不足13施策。達成度の確定には令和6〜8年度の実績が必要です。注2）「第10期での扱い」の先頭の数字は、基本目標を変更した場合の移動先を示します。第9期の基本目標2の施策のうち3件が基本目標1・3へ、基本目標3の4施策すべてが基本目標2へ移ります。注3）第9期の基本目標3（自立支援・介護予防・重度化防止）は、変更案では基本目標名としては残らず、施策はすべて基本目標2へ統合されます。継続評価を重視する場合はこの点が判断材料になります。</t>
+          <t>注1）「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定である。「指標不足」は計画の記載の問題であり、施策そのものの良否を示すものではない。事業が実施され成果を上げている可能性を排除していない（レッドチームレビュー No.11）。判定は素案第9稿 表13による。部分評価可能6施策（1-1・1-3・2-2・3-1・4-2・4-3）、指標不足13施策。達成度の確定には令和6〜8年度の実績が必要です。注2）「第10期での扱い」の先頭の数字は、基本目標を変更した場合の移動先を示します。第9期の基本目標2の施策のうち3件が基本目標1・3へ、基本目標3の4施策すべてが基本目標2へ移ります。注3）第9期の基本目標3（自立支援・介護予防・重度化防止）は、変更案では基本目標名としては残らず、施策はすべて基本目標2へ統合されます。継続評価を重視する場合はこの点が判断材料になります。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_施策体系新旧対照表.xlsx
+++ b/output/第10期計画_施策体系新旧対照表.xlsx
@@ -847,7 +847,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>注1）基本目標3と4で対応関係が大きく変わる点にご留意ください。第9期の「介護予防」は第10期案では基本目標2へ、「サービス基盤」は基本目標3へ移ります。名称を変更する場合、第9期の達成度評価は施策単位で読み替える必要があります。注2）継続を選択した場合でも、各基本目標の下に置く施策は第10期の課題に合わせて再編できます（次シート参照）。注3）素案第9稿では第4章に第10期案、第5章に第9期名称が併存しており、いずれかに統一する必要があります。</t>
+          <t>注1）基本目標3と4で対応関係が大きく変わる点にご留意ください。第9期の「介護予防」は第10期案では基本目標2へ、「サービス基盤」は基本目標3へ移ります。名称を変更する場合、第9期の達成度評価は施策単位で読み替える必要があります。注2）継続を選択した場合でも、各基本目標の下に置く施策は第10期の課題に合わせて再編できます（次シート参照）。注3）計画素案では第4章に第10期案、第5章に第9期名称が併存しており、いずれかに統一する必要があります。</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第9期計画 第5章「施策の展開」の19施策を母数とする。「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定であり、事業が実際に実施されたか、効果があったかを評価したものではない（レッドチームレビュー No.11）。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。判定は素案第9稿 表13による</t>
+          <t>第9期計画 第5章「施策の展開」の19施策を母数とする。「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定であり、事業が実際に実施されたか、効果があったかを評価したものではない（自己点検記録 No.11）。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。判定は計画素案 表13による</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>注1）「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定である。「指標不足」は計画の記載の問題であり、施策そのものの良否を示すものではない。事業が実施され成果を上げている可能性を排除していない（レッドチームレビュー No.11）。判定は素案第9稿 表13による。部分評価可能6施策（1-1・1-3・2-2・3-1・4-2・4-3）、指標不足13施策。達成度の確定には令和6〜8年度の実績が必要です。注2）「第10期での扱い」の先頭の数字は、基本目標を変更した場合の移動先を示します。第9期の基本目標2の施策のうち3件が基本目標1・3へ、基本目標3の4施策すべてが基本目標2へ移ります。注3）第9期の基本目標3（自立支援・介護予防・重度化防止）は、変更案では基本目標名としては残らず、施策はすべて基本目標2へ統合されます。継続評価を重視する場合はこの点が判断材料になります。</t>
+          <t>注1）「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定である。「指標不足」は計画の記載の問題であり、施策そのものの良否を示すものではない。事業が実施され成果を上げている可能性を排除していない（自己点検記録 No.11）。判定は計画素案 表13による。部分評価可能6施策（1-1・1-3・2-2・3-1・4-2・4-3）、指標不足13施策。達成度の確定には令和6〜8年度の実績が必要です。注2）「第10期での扱い」の先頭の数字は、基本目標を変更した場合の移動先を示します。第9期の基本目標2の施策のうち3件が基本目標1・3へ、基本目標3の4施策すべてが基本目標2へ移ります。注3）第9期の基本目標3（自立支援・介護予防・重度化防止）は、変更案では基本目標名としては残らず、施策はすべて基本目標2へ統合されます。継続評価を重視する場合はこの点が判断材料になります。</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>注1）本対照表は第5章「施策の展開」の19施策（18施策＋基本目標5）を母数としています。素案第9稿 表13の「19施策のうち6施策は部分評価可能、13施策は指標不足」もこの母数によります。注2）委員会資料で「19施策」と示す際は、母数の根拠（第5章の本文）を明記してください。体系図の15施策と照らして疑義が生じるおそれがあります。注3）第10期計画では、基本目標の内容・体系図・本文の3か所で施策の記載を一致させることを推奨します。</t>
+          <t>注1）本対照表は第5章「施策の展開」の19施策（18施策＋基本目標5）を母数としています。計画素案 表13の「19施策のうち6施策は部分評価可能、13施策は指標不足」もこの母数によります。注2）委員会資料で「19施策」と示す際は、母数の根拠（第5章の本文）を明記してください。体系図の15施策と照らして疑義が生じるおそれがあります。注3）第10期計画では、基本目標の内容・体系図・本文の3か所で施策の記載を一致させることを推奨します。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_施策体系新旧対照表.xlsx
+++ b/output/第10期計画_施策体系新旧対照表.xlsx
@@ -888,7 +888,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>第9期計画 第5章「施策の展開」の19施策を母数とする。「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定であり、事業が実際に実施されたか、効果があったかを評価したものではない（自己点検記録 No.11）。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。判定は計画素案 表13による</t>
+          <t>第9期計画 第5章「施策の展開」の19施策を母数とする。「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定であり、事業が実際に実施されたか、効果があったかを評価したものではない（受託者の自己点検による）。事業の実施状況の評価は、令和6〜8年度の事業実績の受領後に別に行う。判定は計画素案 表13による</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
     <row r="25" ht="40" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>注1）「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定である。「指標不足」は計画の記載の問題であり、施策そのものの良否を示すものではない。事業が実施され成果を上げている可能性を排除していない（自己点検記録 No.11）。判定は計画素案 表13による。部分評価可能6施策（1-1・1-3・2-2・3-1・4-2・4-3）、指標不足13施策。達成度の確定には令和6〜8年度の実績が必要です。注2）「第10期での扱い」の先頭の数字は、基本目標を変更した場合の移動先を示します。第9期の基本目標2の施策のうち3件が基本目標1・3へ、基本目標3の4施策すべてが基本目標2へ移ります。注3）第9期の基本目標3（自立支援・介護予防・重度化防止）は、変更案では基本目標名としては残らず、施策はすべて基本目標2へ統合されます。継続評価を重視する場合はこの点が判断材料になります。</t>
+          <t>注1）「計画記載上の評価可能性」は、計画に指標と目標が記載されているかどうかの判定である。「指標不足」は計画の記載の問題であり、施策そのものの良否を示すものではない。事業が実施され成果を上げている可能性を排除していない（受託者の自己点検による）。判定は計画素案 表13による。部分評価可能6施策（1-1・1-3・2-2・3-1・4-2・4-3）、指標不足13施策。達成度の確定には令和6〜8年度の実績が必要です。注2）「第10期での扱い」の先頭の数字は、基本目標を変更した場合の移動先を示します。第9期の基本目標2の施策のうち3件が基本目標1・3へ、基本目標3の4施策すべてが基本目標2へ移ります。注3）第9期の基本目標3（自立支援・介護予防・重度化防止）は、変更案では基本目標名としては残らず、施策はすべて基本目標2へ統合されます。継続評価を重視する場合はこの点が判断材料になります。</t>
         </is>
       </c>
     </row>
